--- a/Investigations/Investigation.xlsx
+++ b/Investigations/Investigation.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conor\Documents\College\Masters\Thesis\GeecPE2526\Investigations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE7EED7-B8CF-4402-8430-803D40493799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2205180-FDFF-4D10-905F-B53FC751CB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Consumption" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>Voltage</t>
   </si>
@@ -60,6 +61,102 @@
   </si>
   <si>
     <t>Race Energy</t>
+  </si>
+  <si>
+    <t>FET1</t>
+  </si>
+  <si>
+    <t>RDSon</t>
+  </si>
+  <si>
+    <t>QG</t>
+  </si>
+  <si>
+    <t>Vgs</t>
+  </si>
+  <si>
+    <t>Rg</t>
+  </si>
+  <si>
+    <t>FET2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>PSMN1R2</t>
+  </si>
+  <si>
+    <t>ISG0613N04NM6H</t>
+  </si>
+  <si>
+    <t>FET3</t>
+  </si>
+  <si>
+    <t>IPB014N06N</t>
+  </si>
+  <si>
+    <t>FET4</t>
+  </si>
+  <si>
+    <t>EPC2367</t>
+  </si>
+  <si>
+    <t>Ig</t>
+  </si>
+  <si>
+    <t>QGS2</t>
+  </si>
+  <si>
+    <t>QGD</t>
+  </si>
+  <si>
+    <t>Vin</t>
+  </si>
+  <si>
+    <t>Iout</t>
+  </si>
+  <si>
+    <t>Fsw</t>
+  </si>
+  <si>
+    <t>Psw</t>
+  </si>
+  <si>
+    <t>Pcon</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Irip</t>
+  </si>
+  <si>
+    <t>Duty</t>
+  </si>
+  <si>
+    <t>Pdrv</t>
+  </si>
+  <si>
+    <t>Pbod</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>Vgsth</t>
+  </si>
+  <si>
+    <t>tr(total)</t>
+  </si>
+  <si>
+    <t>tf(total</t>
+  </si>
+  <si>
+    <t>Vf</t>
+  </si>
+  <si>
+    <t>Ptot</t>
   </si>
 </sst>
 </file>
@@ -67,7 +164,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -98,11 +195,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,6 +216,1626 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MOSFET Losses vs Switching Frequency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PSMN1R2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$4:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$Z$4:$Z$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.5794903418913846</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29978103547284618</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.23841727767565538</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25814656941891384</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26944841765202354</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28719547529729506</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.31762114235472849</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34844501110702625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.3794256188243238</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-05B4-48B2-89AA-C039551058D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ISG0613N04NM6H</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$4:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AA$4:$AA$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.53121485006710245</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27483002251677563</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21862602120268412</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23678805530067101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24717882284768822</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26349306902252045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.29146011382516773</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.3197921768481074</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34826791725563017</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-05B4-48B2-89AA-C039551058D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>EPC2367</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$H$4:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AC$4:$AC$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0.71912017736423062</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.36424079434105761</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27180784709456923</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.27025571177364233</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27389752206502938</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.2803530941216188</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.29217142794341056</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.30448751388378276</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.31699952353040467</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-05B4-48B2-89AA-C039551058D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="377905680"/>
+        <c:axId val="377907120"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$20</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>IPB014N06N</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$H$4:$H$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>5000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>10000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>12000</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>15000</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>20000</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>25000</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>30000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$AB$4:$AB$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00E+00</c:formatCode>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>836.00879492493573</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>419.01810273123391</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>302.28542827699738</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>285.65087706924936</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>283.97016507586756</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>282.60742980855525</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>281.5717592673123</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>281.11679953107983</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>280.89041745213882</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-05B4-48B2-89AA-C039551058D8}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="377905680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Switching Frequency (Hz)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="377907120"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="377907120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IE"/>
+                  <a:t>Power Loss (W)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="377905680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>349652</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>192911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>603208</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>157177</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6DD0587-78AC-B591-F4F9-D3C720473D3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20918829" y="385822"/>
+          <a:ext cx="5172797" cy="543001"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>180856</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>156740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>109759</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>96936</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A9CEF27-0F8D-D275-07BB-B3BB8F631F7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21364938" y="1314208"/>
+          <a:ext cx="5463049" cy="3605513"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>506393</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>84399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>298379</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>41512</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C03F7257-A337-BADB-CE8D-BE3D2DFEC3D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22305380" y="4907184"/>
+          <a:ext cx="4096322" cy="1114581"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>611251</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>23758</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B36B6D-6284-727F-6ECD-08D285329F86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16264842" y="6366076"/>
+          <a:ext cx="4915586" cy="3496163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>34964</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>120569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>578733</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>24114</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A52E30F-49B4-B897-033E-3C73959840AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,4 +2181,1135 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D51723-7CEB-4088-9D43-CDD3A744E1FB}">
+  <dimension ref="A1:AC20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1">
+        <v>7.1699999999999995E-5</v>
+      </c>
+      <c r="H4">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="1">
+        <f>$B$1*$B$2*$H4*($B$14+B$15)/$B$3</f>
+        <v>4.3400000000000001E-3</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" ref="J4:L4" si="0">$B$1*$B$2*$H4*($B$14+C$15)/$B$3</f>
+        <v>4.4800000000000005E-3</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>7.1120000000000003E-3</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="0"/>
+        <v>2.464E-3</v>
+      </c>
+      <c r="M4" s="2">
+        <f>$B$1/(4*$B$4*$H4)</f>
+        <v>97.629009762900978</v>
+      </c>
+      <c r="N4" s="1">
+        <f>($B$2^2+$M4^2/12)*B$10*0.5</f>
+        <v>0.57325694189138454</v>
+      </c>
+      <c r="O4" s="1">
+        <f t="shared" ref="O4:Q12" si="1">($B$2^2+$M4^2/12)*C$10*0.5</f>
+        <v>0.52548553006710241</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="1"/>
+        <v>835.99970692493571</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="1"/>
+        <v>0.71657117736423059</v>
+      </c>
+      <c r="R4" s="1">
+        <f>B$11*B$12*$H4</f>
+        <v>7.000000000000001E-4</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" ref="S4:U12" si="2">C$11*C$12*$H4</f>
+        <v>6.8999999999999997E-4</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" si="2"/>
+        <v>8.5000000000000006E-5</v>
+      </c>
+      <c r="V4" s="1">
+        <f>B$19*$B$2*(B$17+B$18)*$H4</f>
+        <v>1.1934000000000001E-3</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" ref="W4:Y4" si="3">C$19*$B$2*(C$17+C$18)*$H4</f>
+        <v>5.5931999999999998E-4</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="3"/>
+        <v>9.3599999999999998E-4</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1">
+        <f>I4+N4+R4+V4</f>
+        <v>0.5794903418913846</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" ref="AA4:AC12" si="4">J4+O4+S4+W4</f>
+        <v>0.53121485006710245</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="4"/>
+        <v>836.00879492493573</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.71912017736423062</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.25</v>
+      </c>
+      <c r="H5">
+        <v>2000</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" ref="I5:I9" si="5">$B$1*$B$2*$H5*($B$14+B$15)/$B$3</f>
+        <v>8.6800000000000002E-3</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" ref="J5:J9" si="6">$B$1*$B$2*$H5*($B$14+C$15)/$B$3</f>
+        <v>8.9600000000000009E-3</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" ref="K5:K9" si="7">$B$1*$B$2*$H5*($B$14+D$15)/$B$3</f>
+        <v>1.4224000000000001E-2</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" ref="L5:L9" si="8">$B$1*$B$2*$H5*($B$14+E$15)/$B$3</f>
+        <v>4.9280000000000001E-3</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" ref="M5:M9" si="9">$B$1/(4*$B$4*$H5)</f>
+        <v>48.814504881450489</v>
+      </c>
+      <c r="N5" s="1">
+        <f t="shared" ref="N5:N12" si="10">($B$2^2+$M5^2/12)*B$10*0.5</f>
+        <v>0.28731423547284612</v>
+      </c>
+      <c r="O5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.26337138251677561</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="1"/>
+        <v>418.99992673123393</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.35914279434105761</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" ref="R5:R12" si="11">B$11*B$12*$H5</f>
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.3799999999999999E-3</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" si="2"/>
+        <v>2.0799999999999998E-3</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" si="2"/>
+        <v>1.7000000000000001E-4</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" ref="V5:V12" si="12">B$19*$B$2*(B$17+B$18)*$H5</f>
+        <v>2.3868000000000001E-3</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" ref="W5:W12" si="13">C$19*$B$2*(C$17+C$18)*$H5</f>
+        <v>1.11864E-3</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" ref="X5:X12" si="14">D$19*$B$2*(D$17+D$18)*$H5</f>
+        <v>1.872E-3</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ref="Y5:Y12" si="15">E$19*$B$2*(E$17+E$18)*$H5</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" ref="Z5:Z12" si="16">I5+N5+R5+V5</f>
+        <v>0.29978103547284618</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="4"/>
+        <v>0.27483002251677563</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="4"/>
+        <v>419.01810273123391</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="4"/>
+        <v>0.36424079434105761</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1E-8</v>
+      </c>
+      <c r="H6">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="5"/>
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="6"/>
+        <v>2.24E-2</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="7"/>
+        <v>3.5560000000000001E-2</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="8"/>
+        <v>1.2319999999999999E-2</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="9"/>
+        <v>19.525801952580196</v>
+      </c>
+      <c r="N6" s="1">
+        <f t="shared" si="10"/>
+        <v>0.20725027767565538</v>
+      </c>
+      <c r="O6" s="1">
+        <f t="shared" si="1"/>
+        <v>0.1899794212026841</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="1"/>
+        <v>302.23998827699739</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="1"/>
+        <v>0.25906284709456923</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="11"/>
+        <v>3.5000000000000005E-3</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="2"/>
+        <v>3.4499999999999999E-3</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" si="2"/>
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" si="2"/>
+        <v>4.2500000000000003E-4</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" si="12"/>
+        <v>5.9670000000000001E-3</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="13"/>
+        <v>2.7966000000000002E-3</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="14"/>
+        <v>4.6800000000000001E-3</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="16"/>
+        <v>0.23841727767565538</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.21862602120268412</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="4"/>
+        <v>302.28542827699738</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.27180784709456923</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>10000</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="5"/>
+        <v>4.3400000000000001E-2</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="6"/>
+        <v>4.48E-2</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="7"/>
+        <v>7.1120000000000003E-2</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="8"/>
+        <v>2.4639999999999999E-2</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="9"/>
+        <v>9.7629009762900978</v>
+      </c>
+      <c r="N7" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19581256941891384</v>
+      </c>
+      <c r="O7" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17949485530067102</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="1"/>
+        <v>285.55999706924933</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24476571177364229</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="11"/>
+        <v>7.000000000000001E-3</v>
+      </c>
+      <c r="S7" s="1">
+        <f t="shared" si="2"/>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" si="2"/>
+        <v>1.04E-2</v>
+      </c>
+      <c r="U7" s="1">
+        <f t="shared" si="2"/>
+        <v>8.5000000000000006E-4</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" si="12"/>
+        <v>1.1934E-2</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" si="13"/>
+        <v>5.5932000000000004E-3</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" si="14"/>
+        <v>9.3600000000000003E-3</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" si="16"/>
+        <v>0.25814656941891384</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.23678805530067101</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" si="4"/>
+        <v>285.65087706924936</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.27025571177364233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>12000</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="5"/>
+        <v>5.2080000000000001E-2</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="6"/>
+        <v>5.3760000000000002E-2</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="7"/>
+        <v>8.5344000000000003E-2</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="8"/>
+        <v>2.9567999999999997E-2</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="9"/>
+        <v>8.1357508135750827</v>
+      </c>
+      <c r="N8" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19464761765202349</v>
+      </c>
+      <c r="O8" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17842698284768821</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="1"/>
+        <v>283.86110907586755</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24330952206502934</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="11"/>
+        <v>8.4000000000000012E-3</v>
+      </c>
+      <c r="S8" s="1">
+        <f t="shared" si="2"/>
+        <v>8.2799999999999992E-3</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" si="2"/>
+        <v>1.248E-2</v>
+      </c>
+      <c r="U8" s="1">
+        <f t="shared" si="2"/>
+        <v>1.0200000000000001E-3</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" si="12"/>
+        <v>1.4320800000000002E-2</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="13"/>
+        <v>6.7118400000000002E-3</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" si="14"/>
+        <v>1.1232000000000001E-2</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" si="16"/>
+        <v>0.26944841765202354</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="4"/>
+        <v>0.24717882284768822</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="4"/>
+        <v>283.97016507586756</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="4"/>
+        <v>0.27389752206502938</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>15000</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="5"/>
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="6"/>
+        <v>6.720000000000001E-2</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="7"/>
+        <v>0.10668000000000001</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="8"/>
+        <v>3.696E-2</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="9"/>
+        <v>6.5086006508600658</v>
+      </c>
+      <c r="N9" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19369447529729503</v>
+      </c>
+      <c r="O9" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17755326902252044</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="1"/>
+        <v>282.47110980855524</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24211809412161878</v>
+      </c>
+      <c r="R9" s="1">
+        <f t="shared" si="11"/>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="S9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.035E-2</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="U9" s="1">
+        <f t="shared" si="2"/>
+        <v>1.2750000000000001E-3</v>
+      </c>
+      <c r="V9" s="1">
+        <f t="shared" si="12"/>
+        <v>1.7901E-2</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" si="13"/>
+        <v>8.3897999999999993E-3</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" si="14"/>
+        <v>1.404E-2</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="16"/>
+        <v>0.28719547529729506</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" si="4"/>
+        <v>0.26349306902252045</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" si="4"/>
+        <v>282.60742980855525</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="4"/>
+        <v>0.2803530941216188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.6000000000000002E-4</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8.8000000000000003E-4</v>
+      </c>
+      <c r="D10">
+        <v>1.4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="H10">
+        <v>20000</v>
+      </c>
+      <c r="I10" s="1">
+        <f>$B$1*$B$2*$H10*($B$14+B$15)/$B$3</f>
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="J10" s="1">
+        <f>$B$1*$B$2*$H10*($B$14+C$15)/$B$3</f>
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="K10" s="1">
+        <f>$B$1*$B$2*$H10*($B$14+D$15)/$B$3</f>
+        <v>0.14224000000000001</v>
+      </c>
+      <c r="L10" s="1">
+        <f>$B$1*$B$2*$H10*($B$14+E$15)/$B$3</f>
+        <v>4.9279999999999997E-2</v>
+      </c>
+      <c r="M10" s="2">
+        <f>$B$1/(4*$B$4*$H10)</f>
+        <v>4.8814504881450489</v>
+      </c>
+      <c r="N10" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19295314235472846</v>
+      </c>
+      <c r="O10" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17687371382516776</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="1"/>
+        <v>281.38999926731231</v>
+      </c>
+      <c r="Q10" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24119142794341056</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="11"/>
+        <v>1.4000000000000002E-2</v>
+      </c>
+      <c r="S10" s="1">
+        <f t="shared" si="2"/>
+        <v>1.38E-2</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" si="2"/>
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" si="2"/>
+        <v>1.7000000000000001E-3</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" si="12"/>
+        <v>2.3868E-2</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="13"/>
+        <v>1.1186400000000001E-2</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" si="14"/>
+        <v>1.8720000000000001E-2</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="16"/>
+        <v>0.31762114235472849</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" si="4"/>
+        <v>0.29146011382516773</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" si="4"/>
+        <v>281.5717592673123</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="4"/>
+        <v>0.29217142794341056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7.0000000000000005E-8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6.8999999999999996E-8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1.04E-7</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.7E-8</v>
+      </c>
+      <c r="H11" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I11" s="1">
+        <f>$B$1*$B$2*$H11*($B$14+B$15)/$B$3</f>
+        <v>0.1085</v>
+      </c>
+      <c r="J11" s="1">
+        <f>$B$1*$B$2*$H11*($B$14+C$15)/$B$3</f>
+        <v>0.112</v>
+      </c>
+      <c r="K11" s="1">
+        <f>$B$1*$B$2*$H11*($B$14+D$15)/$B$3</f>
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="L11" s="1">
+        <f>$B$1*$B$2*$H11*($B$14+E$15)/$B$3</f>
+        <v>6.1599999999999995E-2</v>
+      </c>
+      <c r="M11" s="2">
+        <f>$B$1/(4*$B$4*$H11)</f>
+        <v>3.9051603905160395</v>
+      </c>
+      <c r="N11" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19261001110702622</v>
+      </c>
+      <c r="O11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17655917684810737</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="1"/>
+        <v>280.88959953107985</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24076251388378275</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="11"/>
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="S11" s="1">
+        <f t="shared" si="2"/>
+        <v>1.7249999999999998E-2</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" si="2"/>
+        <v>2.1250000000000002E-3</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" si="12"/>
+        <v>2.9835E-2</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="13"/>
+        <v>1.3983000000000001E-2</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="14"/>
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="16"/>
+        <v>0.34844501110702625</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="4"/>
+        <v>0.3197921768481074</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" si="4"/>
+        <v>281.11679953107983</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="4"/>
+        <v>0.30448751388378276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>30000</v>
+      </c>
+      <c r="I12" s="1">
+        <f>$B$1*$B$2*$H12*($B$14+B$15)/$B$3</f>
+        <v>0.13020000000000001</v>
+      </c>
+      <c r="J12" s="1">
+        <f>$B$1*$B$2*$H12*($B$14+C$15)/$B$3</f>
+        <v>0.13440000000000002</v>
+      </c>
+      <c r="K12" s="1">
+        <f>$B$1*$B$2*$H12*($B$14+D$15)/$B$3</f>
+        <v>0.21336000000000002</v>
+      </c>
+      <c r="L12" s="1">
+        <f>$B$1*$B$2*$H12*($B$14+E$15)/$B$3</f>
+        <v>7.392E-2</v>
+      </c>
+      <c r="M12" s="2">
+        <f>$B$1/(4*$B$4*$H12)</f>
+        <v>3.2543003254300329</v>
+      </c>
+      <c r="N12" s="1">
+        <f t="shared" si="10"/>
+        <v>0.19242361882432377</v>
+      </c>
+      <c r="O12" s="1">
+        <f t="shared" si="1"/>
+        <v>0.17638831725563012</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" si="1"/>
+        <v>280.6177774521388</v>
+      </c>
+      <c r="Q12" s="1">
+        <f t="shared" si="1"/>
+        <v>0.24052952353040469</v>
+      </c>
+      <c r="R12" s="1">
+        <f t="shared" si="11"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="S12" s="1">
+        <f t="shared" si="2"/>
+        <v>2.07E-2</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" si="2"/>
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" si="2"/>
+        <v>2.5500000000000002E-3</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" si="12"/>
+        <v>3.5802E-2</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="13"/>
+        <v>1.6779599999999999E-2</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" si="14"/>
+        <v>2.8080000000000001E-2</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="16"/>
+        <v>0.3794256188243238</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" si="4"/>
+        <v>0.34826791725563017</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" si="4"/>
+        <v>280.89041745213882</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" si="4"/>
+        <v>0.31699952353040467</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1.6</v>
+      </c>
+      <c r="E13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6.4000000000000002E-9</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.0999999999999999E-8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2.1999999999999998E-8</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3.8000000000000001E-9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1">
+        <v>9.1000000000000004E-9</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9.5999999999999999E-9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.9000000000000001E-8</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2.4E-9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1">
+        <f>$B$6+0.000000031</f>
+        <v>4.0999999999999997E-8</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" ref="C17:E17" si="17">$B$6+0.0000000093</f>
+        <v>1.9300000000000001E-8</v>
+      </c>
+      <c r="D17" s="1">
+        <f>$B$6+0.000000018</f>
+        <v>2.7999999999999999E-8</v>
+      </c>
+      <c r="E17" s="1">
+        <f>$B$6</f>
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1">
+        <f>$B$6+0.0000000255</f>
+        <v>3.55E-8</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" ref="C18:E18" si="18">$B$6+0.0000000061</f>
+        <v>1.6099999999999999E-8</v>
+      </c>
+      <c r="D18" s="1">
+        <f>$B$6+0.000000014</f>
+        <v>2.4E-8</v>
+      </c>
+      <c r="E18" s="1">
+        <f>$B$6</f>
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>0.78</v>
+      </c>
+      <c r="C19">
+        <v>0.79</v>
+      </c>
+      <c r="D19">
+        <v>0.9</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Investigations/Investigation.xlsx
+++ b/Investigations/Investigation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conor\Documents\College\Masters\Thesis\GeecPE2526\Investigations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Masters\Project\Investigations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2205180-FDFF-4D10-905F-B53FC751CB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B213A0-2F9F-4800-AA9C-2067E06547C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Consumption" sheetId="1" r:id="rId1"/>
@@ -195,12 +195,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1801,16 +1800,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>34964</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>120569</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>119362</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>60284</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>578733</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>24114</xdr:rowOff>
+      <xdr:colOff>48226</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>156739</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2883,19 +2882,19 @@
         <v>20000</v>
       </c>
       <c r="I10" s="1">
-        <f>$B$1*$B$2*$H10*($B$14+B$15)/$B$3</f>
+        <f t="shared" ref="I10:L12" si="17">$B$1*$B$2*$H10*($B$14+B$15)/$B$3</f>
         <v>8.6800000000000002E-2</v>
       </c>
       <c r="J10" s="1">
-        <f>$B$1*$B$2*$H10*($B$14+C$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>8.9599999999999999E-2</v>
       </c>
       <c r="K10" s="1">
-        <f>$B$1*$B$2*$H10*($B$14+D$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.14224000000000001</v>
       </c>
       <c r="L10" s="1">
-        <f>$B$1*$B$2*$H10*($B$14+E$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>4.9279999999999997E-2</v>
       </c>
       <c r="M10" s="2">
@@ -2983,23 +2982,23 @@
       <c r="E11" s="1">
         <v>1.7E-8</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11">
         <v>25000</v>
       </c>
       <c r="I11" s="1">
-        <f>$B$1*$B$2*$H11*($B$14+B$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.1085</v>
       </c>
       <c r="J11" s="1">
-        <f>$B$1*$B$2*$H11*($B$14+C$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.112</v>
       </c>
       <c r="K11" s="1">
-        <f>$B$1*$B$2*$H11*($B$14+D$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.17780000000000001</v>
       </c>
       <c r="L11" s="1">
-        <f>$B$1*$B$2*$H11*($B$14+E$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>6.1599999999999995E-2</v>
       </c>
       <c r="M11" s="2">
@@ -3091,19 +3090,19 @@
         <v>30000</v>
       </c>
       <c r="I12" s="1">
-        <f>$B$1*$B$2*$H12*($B$14+B$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.13020000000000001</v>
       </c>
       <c r="J12" s="1">
-        <f>$B$1*$B$2*$H12*($B$14+C$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.13440000000000002</v>
       </c>
       <c r="K12" s="1">
-        <f>$B$1*$B$2*$H12*($B$14+D$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>0.21336000000000002</v>
       </c>
       <c r="L12" s="1">
-        <f>$B$1*$B$2*$H12*($B$14+E$15)/$B$3</f>
+        <f t="shared" si="17"/>
         <v>7.392E-2</v>
       </c>
       <c r="M12" s="2">
@@ -3240,7 +3239,7 @@
         <v>4.0999999999999997E-8</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" ref="C17:E17" si="17">$B$6+0.0000000093</f>
+        <f t="shared" ref="C17" si="18">$B$6+0.0000000093</f>
         <v>1.9300000000000001E-8</v>
       </c>
       <c r="D17" s="1">
@@ -3261,7 +3260,7 @@
         <v>3.55E-8</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="18">$B$6+0.0000000061</f>
+        <f t="shared" ref="C18" si="19">$B$6+0.0000000061</f>
         <v>1.6099999999999999E-8</v>
       </c>
       <c r="D18" s="1">
